--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.55245745865654</v>
+        <v>6.264774337031688</v>
       </c>
       <c r="D2" t="n">
-        <v>38.42511426390777</v>
+        <v>6.244081067885012</v>
       </c>
       <c r="E2" t="n">
-        <v>23.46515910369045</v>
+        <v>3.813088354349698</v>
       </c>
       <c r="F2" t="n">
-        <v>23.50685441233463</v>
+        <v>3.819863842004378</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.32743467631445</v>
+        <v>6.553208134901098</v>
       </c>
       <c r="D3" t="n">
-        <v>40.36203180955505</v>
+        <v>6.558830169052696</v>
       </c>
       <c r="E3" t="n">
-        <v>23.46515910369045</v>
+        <v>3.813088354349698</v>
       </c>
       <c r="F3" t="n">
-        <v>23.50685441233463</v>
+        <v>3.819863842004378</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>76.92143239210502</v>
+        <v>12.49973276371707</v>
       </c>
       <c r="D4" t="n">
-        <v>77.01207714689339</v>
+        <v>12.51446253637018</v>
       </c>
       <c r="E4" t="n">
-        <v>23.46515910369045</v>
+        <v>3.813088354349698</v>
       </c>
       <c r="F4" t="n">
-        <v>23.50685441233463</v>
+        <v>3.819863842004378</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.93453197403644</v>
+        <v>6.489361445780921</v>
       </c>
       <c r="D5" t="n">
-        <v>40.06168951182273</v>
+        <v>6.510024545671193</v>
       </c>
       <c r="E5" t="n">
-        <v>23.46515910369045</v>
+        <v>3.813088354349698</v>
       </c>
       <c r="F5" t="n">
-        <v>23.50685441233463</v>
+        <v>3.819863842004378</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>95.12557957049584</v>
+        <v>15.45790668020557</v>
       </c>
       <c r="D6" t="n">
-        <v>95.22338009805028</v>
+        <v>15.47379926593317</v>
       </c>
       <c r="E6" t="n">
-        <v>23.46515910369045</v>
+        <v>3.813088354349698</v>
       </c>
       <c r="F6" t="n">
-        <v>23.50685441233463</v>
+        <v>3.819863842004378</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
